--- a/Wrażliwość.xlsx
+++ b/Wrażliwość.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prac608\Desktop\BO_KW1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1213170-0552-4B16-8ED0-AE5255F39C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4A5566-EAE8-4DBC-9E5C-58C452D503B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{687A66AF-72A4-48D0-9912-68F333D303E6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{687A66AF-72A4-48D0-9912-68F333D303E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
+    <sheet name="Arkusz2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,8 +37,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="137">
   <si>
     <t>Rozwiązać zadanie metodą simplex</t>
   </si>
@@ -277,6 +300,177 @@
   </si>
   <si>
     <t>&lt;=C2&lt;=</t>
+  </si>
+  <si>
+    <t>Punkt wyjścia do analizy wrażliwosći</t>
+  </si>
+  <si>
+    <t>tablica z rozwiązaniem optymalnym</t>
+  </si>
+  <si>
+    <t>2. Badanie wrażliwości rozwiązania optymalnego na zmiane w wyrazie wolnym 1 WO</t>
+  </si>
+  <si>
+    <t>E1-dopuszca;na zmiana w wyrazie wolnym 1 WO</t>
+  </si>
+  <si>
+    <t>wektor wyrazów wolnych</t>
+  </si>
+  <si>
+    <t>wektor po zmianie</t>
+  </si>
+  <si>
+    <t>bi'1</t>
+  </si>
+  <si>
+    <t>40+E1</t>
+  </si>
+  <si>
+    <t>Macierz B^-1 w rozwiązaniu optymalnym</t>
+  </si>
+  <si>
+    <t>3. Zapis warunku optymalności rozwiązania i rozwiązanie układu nierówności</t>
+  </si>
+  <si>
+    <t>B^-1*b'1&gt;=0</t>
+  </si>
+  <si>
+    <t>pomnożyć macierze</t>
+  </si>
+  <si>
+    <t>4+0,4E1</t>
+  </si>
+  <si>
+    <t>6-0,15E1</t>
+  </si>
+  <si>
+    <t>-0,35E1</t>
+  </si>
+  <si>
+    <t>4+0,4E1&gt;=0</t>
+  </si>
+  <si>
+    <t>6-0,15E1&gt;=0</t>
+  </si>
+  <si>
+    <t>4-0,35E1&gt;=0</t>
+  </si>
+  <si>
+    <t>E1&gt;=</t>
+  </si>
+  <si>
+    <t>E1&lt;=</t>
+  </si>
+  <si>
+    <t>Nierówności</t>
+  </si>
+  <si>
+    <t>Część wspólna</t>
+  </si>
+  <si>
+    <t>&lt;=E1&lt;=</t>
+  </si>
+  <si>
+    <t>Granice zmian wyrazu wolnego Wo1 to</t>
+  </si>
+  <si>
+    <t>b1</t>
+  </si>
+  <si>
+    <t>Górna granica</t>
+  </si>
+  <si>
+    <t>Dolna granica</t>
+  </si>
+  <si>
+    <t>2 warunek WO2</t>
+  </si>
+  <si>
+    <t>30+E2</t>
+  </si>
+  <si>
+    <t>-0,2E2</t>
+  </si>
+  <si>
+    <t>+0,45E2</t>
+  </si>
+  <si>
+    <t>+0,05E2</t>
+  </si>
+  <si>
+    <t>4-0,2E2&gt;=0</t>
+  </si>
+  <si>
+    <t>6+0,45E2&gt;=0</t>
+  </si>
+  <si>
+    <t>4+0,05E2&gt;=0</t>
+  </si>
+  <si>
+    <t>E2&lt;=</t>
+  </si>
+  <si>
+    <t>E2&gt;=</t>
+  </si>
+  <si>
+    <t>&lt;=E2&lt;=</t>
+  </si>
+  <si>
+    <t>Granice zmian wyrazu wolnego WO2</t>
+  </si>
+  <si>
+    <t>3 warunek WO3</t>
+  </si>
+  <si>
+    <t>bi'2</t>
+  </si>
+  <si>
+    <t>30+E3</t>
+  </si>
+  <si>
+    <t>-0,2E3</t>
+  </si>
+  <si>
+    <t>&gt;=0</t>
+  </si>
+  <si>
+    <t>-0,05E3</t>
+  </si>
+  <si>
+    <t>+0,55E3</t>
+  </si>
+  <si>
+    <t>E3&lt;=</t>
+  </si>
+  <si>
+    <t>E3&gt;=</t>
+  </si>
+  <si>
+    <t>&lt;=E3&lt;=</t>
+  </si>
+  <si>
+    <t>Granice zmian wyrazu wolnego WO3</t>
+  </si>
+  <si>
+    <t>bi'3</t>
+  </si>
+  <si>
+    <t>Etap4</t>
+  </si>
+  <si>
+    <t>Wyznaczamy wartości zmiennych w rozwiązaniu optymalnym , zmienia się też wartość funkcji celu</t>
+  </si>
+  <si>
+    <t>dolna granica</t>
+  </si>
+  <si>
+    <t>Fc=</t>
+  </si>
+  <si>
+    <t>dolna</t>
+  </si>
+  <si>
+    <t>górna</t>
   </si>
 </sst>
 </file>
@@ -314,7 +508,7 @@
       <charset val="238"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -336,6 +530,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -378,7 +578,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -429,6 +629,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -2387,4 +2591,1220 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C57C990E-2D49-455D-840C-F8477A51AAAB}">
+  <dimension ref="B2:Q80"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="11" max="11" width="9.8984375" customWidth="1"/>
+    <col min="14" max="14" width="20.09765625" customWidth="1"/>
+    <col min="15" max="15" width="12.19921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:15">
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2">
+        <v>32</v>
+      </c>
+      <c r="E2">
+        <v>24</v>
+      </c>
+      <c r="F2">
+        <v>48</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15">
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15">
+      <c r="B4">
+        <v>48</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" s="31">
+        <v>0.40000000000000008</v>
+      </c>
+      <c r="H4" s="31">
+        <v>-0.2</v>
+      </c>
+      <c r="I4" s="31">
+        <v>-0.2</v>
+      </c>
+      <c r="J4">
+        <v>3.9999999999999991</v>
+      </c>
+      <c r="N4" t="s">
+        <v>5</v>
+      </c>
+      <c r="O4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15">
+      <c r="B5">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="31">
+        <v>-0.15000000000000002</v>
+      </c>
+      <c r="H5" s="31">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="I5" s="31">
+        <v>-4.9999999999999989E-2</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="O5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15">
+      <c r="B6">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" s="31">
+        <v>-0.35000000000000009</v>
+      </c>
+      <c r="H6" s="31">
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="I6" s="31">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J6">
+        <v>4.0000000000000009</v>
+      </c>
+      <c r="O6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15">
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7">
+        <v>32</v>
+      </c>
+      <c r="E7">
+        <v>24</v>
+      </c>
+      <c r="F7">
+        <v>48</v>
+      </c>
+      <c r="G7">
+        <v>4.3999999999999986</v>
+      </c>
+      <c r="H7">
+        <v>2.7999999999999989</v>
+      </c>
+      <c r="I7">
+        <v>6.8000000000000007</v>
+      </c>
+      <c r="J7">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15">
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>-4.3999999999999986</v>
+      </c>
+      <c r="H8">
+        <v>-2.7999999999999989</v>
+      </c>
+      <c r="I8">
+        <v>-6.8000000000000007</v>
+      </c>
+      <c r="N8" t="s">
+        <v>9</v>
+      </c>
+      <c r="O8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15">
+      <c r="B10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15">
+      <c r="B12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15">
+      <c r="B13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15">
+      <c r="B14" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="4">
+        <v>40</v>
+      </c>
+      <c r="F14" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15">
+      <c r="C15" s="4">
+        <v>30</v>
+      </c>
+      <c r="G15" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15">
+      <c r="C16" s="4">
+        <v>30</v>
+      </c>
+      <c r="G16" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17">
+      <c r="B17" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="G17" s="30" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17">
+      <c r="B19" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17">
+      <c r="B21" s="31">
+        <v>0.40000000000000008</v>
+      </c>
+      <c r="C21" s="31">
+        <v>-0.2</v>
+      </c>
+      <c r="D21" s="31">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17">
+      <c r="B22" s="31">
+        <v>-0.15000000000000002</v>
+      </c>
+      <c r="C22" s="31">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="D22" s="31">
+        <v>-4.9999999999999989E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17">
+      <c r="B23" s="31">
+        <v>-0.35000000000000009</v>
+      </c>
+      <c r="C23" s="31">
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="D23" s="31">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17">
+      <c r="B25" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17">
+      <c r="J26" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="K26" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17">
+      <c r="B27" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17">
+      <c r="F28" t="s">
+        <v>87</v>
+      </c>
+      <c r="K28" t="s">
+        <v>133</v>
+      </c>
+      <c r="M28">
+        <f>H43</f>
+        <v>30</v>
+      </c>
+      <c r="O28" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q28" s="22">
+        <f>H42</f>
+        <v>51.428571428571431</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17">
+      <c r="B29" t="s">
+        <v>91</v>
+      </c>
+      <c r="F29">
+        <v>30</v>
+      </c>
+      <c r="M29">
+        <v>30</v>
+      </c>
+      <c r="Q29" s="22">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17">
+      <c r="F30">
+        <v>30</v>
+      </c>
+      <c r="M30">
+        <v>30</v>
+      </c>
+      <c r="Q30" s="22">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17">
+      <c r="C31">
+        <v>0.40000000000000008</v>
+      </c>
+      <c r="D31">
+        <v>-0.2</v>
+      </c>
+      <c r="E31">
+        <v>-0.2</v>
+      </c>
+      <c r="F31" s="29" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17">
+      <c r="C32">
+        <v>-0.15000000000000002</v>
+      </c>
+      <c r="D32">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="E32">
+        <v>-4.9999999999999989E-2</v>
+      </c>
+      <c r="F32" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="K32" s="31">
+        <v>0.40000000000000008</v>
+      </c>
+      <c r="L32" s="31">
+        <v>-0.2</v>
+      </c>
+      <c r="M32" s="31">
+        <v>-0.2</v>
+      </c>
+      <c r="O32" s="31">
+        <v>0.40000000000000008</v>
+      </c>
+      <c r="P32" s="31">
+        <v>-0.2</v>
+      </c>
+      <c r="Q32" s="31">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17">
+      <c r="C33">
+        <v>-0.35000000000000009</v>
+      </c>
+      <c r="D33">
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="E33">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F33" s="29">
+        <f>C33*40+D33*F29+E33*F30</f>
+        <v>3.9999999999999982</v>
+      </c>
+      <c r="G33" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="K33" s="31">
+        <v>-0.15000000000000002</v>
+      </c>
+      <c r="L33" s="31">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="M33" s="31">
+        <v>-4.9999999999999989E-2</v>
+      </c>
+      <c r="O33" s="31">
+        <v>-0.15000000000000002</v>
+      </c>
+      <c r="P33" s="31">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="Q33" s="31">
+        <v>-4.9999999999999989E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17">
+      <c r="C34" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="K34" s="31">
+        <v>-0.35000000000000009</v>
+      </c>
+      <c r="L34" s="31">
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="M34" s="31">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="O34" s="31">
+        <v>-0.35000000000000009</v>
+      </c>
+      <c r="P34" s="31">
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="Q34" s="31">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17">
+      <c r="C35" s="30">
+        <v>1</v>
+      </c>
+      <c r="D35" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="F35" t="s">
+        <v>98</v>
+      </c>
+      <c r="G35">
+        <f>-4/0.4</f>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="36" spans="2:17">
+      <c r="C36" s="30">
+        <v>2</v>
+      </c>
+      <c r="D36" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G36">
+        <f>-6/-0.15</f>
+        <v>40</v>
+      </c>
+      <c r="K36" s="22" cm="1">
+        <f t="array" ref="K36:K38">MMULT(K32:M34,M28:M30)</f>
+        <v>1.7763568394002505E-15</v>
+      </c>
+      <c r="L36" t="s">
+        <v>13</v>
+      </c>
+      <c r="O36" s="22" cm="1">
+        <f t="array" ref="O36:O38">MMULT(O32:Q34,Q28:Q30)</f>
+        <v>8.5714285714285765</v>
+      </c>
+      <c r="P36" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17">
+      <c r="C37" s="30">
+        <v>3</v>
+      </c>
+      <c r="D37" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G37" s="22">
+        <f>-4/-0.35</f>
+        <v>11.428571428571429</v>
+      </c>
+      <c r="K37" s="22">
+        <v>7.4999999999999964</v>
+      </c>
+      <c r="L37" t="s">
+        <v>12</v>
+      </c>
+      <c r="O37" s="22">
+        <v>4.2857142857142829</v>
+      </c>
+      <c r="P37" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="2:17">
+      <c r="K38" s="22">
+        <v>7.4999999999999982</v>
+      </c>
+      <c r="L38" t="s">
+        <v>11</v>
+      </c>
+      <c r="O38" s="22">
+        <v>-3.5527136788005009E-15</v>
+      </c>
+      <c r="P38" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17">
+      <c r="C39" t="s">
+        <v>101</v>
+      </c>
+      <c r="E39">
+        <f>G35</f>
+        <v>-10</v>
+      </c>
+      <c r="F39" t="s">
+        <v>102</v>
+      </c>
+      <c r="G39" s="22">
+        <f>G37</f>
+        <v>11.428571428571429</v>
+      </c>
+    </row>
+    <row r="40" spans="2:17">
+      <c r="K40" t="s">
+        <v>134</v>
+      </c>
+      <c r="L40" s="33">
+        <f>32*K38+24*K37+48*K36</f>
+        <v>420</v>
+      </c>
+      <c r="O40" t="s">
+        <v>134</v>
+      </c>
+      <c r="P40" s="32">
+        <f>32*O38+24*O37+48*O36</f>
+        <v>514.28571428571433</v>
+      </c>
+    </row>
+    <row r="41" spans="2:17">
+      <c r="C41" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17">
+      <c r="C42" t="s">
+        <v>104</v>
+      </c>
+      <c r="D42">
+        <v>40</v>
+      </c>
+      <c r="F42" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="H42" s="32">
+        <f>D42+G39</f>
+        <v>51.428571428571431</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17">
+      <c r="F43" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="H43" s="33">
+        <f>D42+E39</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17">
+      <c r="B45" s="30" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17">
+      <c r="B47" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" s="4">
+        <v>40</v>
+      </c>
+      <c r="E47" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="F47" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17">
+      <c r="C48" s="4">
+        <v>30</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="49" spans="2:17">
+      <c r="C49" s="4">
+        <v>30</v>
+      </c>
+      <c r="F49" s="4">
+        <v>30</v>
+      </c>
+      <c r="J49" t="s">
+        <v>135</v>
+      </c>
+      <c r="K49">
+        <v>40</v>
+      </c>
+      <c r="O49" t="s">
+        <v>136</v>
+      </c>
+      <c r="P49">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="50" spans="2:17">
+      <c r="K50" s="22">
+        <f>D62</f>
+        <v>16.666666666666668</v>
+      </c>
+      <c r="P50">
+        <f>D63</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="2:17">
+      <c r="B51" s="31">
+        <v>0.40000000000000008</v>
+      </c>
+      <c r="C51" s="31">
+        <v>-0.2</v>
+      </c>
+      <c r="D51" s="31">
+        <v>-0.2</v>
+      </c>
+      <c r="F51">
+        <f>B51*F47+C51*30+D51*F49</f>
+        <v>4.0000000000000036</v>
+      </c>
+      <c r="G51" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="K51">
+        <v>30</v>
+      </c>
+      <c r="P51">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="52" spans="2:17">
+      <c r="B52" s="31">
+        <v>-0.15000000000000002</v>
+      </c>
+      <c r="C52" s="31">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="D52" s="31">
+        <v>-4.9999999999999989E-2</v>
+      </c>
+      <c r="F52">
+        <f>B52*F47+C52*30+D52*F49</f>
+        <v>5.9999999999999982</v>
+      </c>
+      <c r="G52" s="21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="53" spans="2:17">
+      <c r="B53" s="31">
+        <v>-0.35000000000000009</v>
+      </c>
+      <c r="C53" s="31">
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="D53" s="31">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F53">
+        <f>B53*F47+C53*30+D53*F49</f>
+        <v>3.9999999999999982</v>
+      </c>
+      <c r="G53" s="21" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="54" spans="2:17">
+      <c r="J54" s="31">
+        <v>0.40000000000000008</v>
+      </c>
+      <c r="K54" s="31">
+        <v>-0.2</v>
+      </c>
+      <c r="L54" s="31">
+        <v>-0.2</v>
+      </c>
+      <c r="O54" s="31">
+        <v>0.40000000000000008</v>
+      </c>
+      <c r="P54" s="31">
+        <v>-0.2</v>
+      </c>
+      <c r="Q54" s="31">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="55" spans="2:17">
+      <c r="C55" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="J55" s="31">
+        <v>-0.15000000000000002</v>
+      </c>
+      <c r="K55" s="31">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="L55" s="31">
+        <v>-4.9999999999999989E-2</v>
+      </c>
+      <c r="O55" s="31">
+        <v>-0.15000000000000002</v>
+      </c>
+      <c r="P55" s="31">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="Q55" s="31">
+        <v>-4.9999999999999989E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="2:17">
+      <c r="B56" s="1">
+        <v>1</v>
+      </c>
+      <c r="C56" t="s">
+        <v>112</v>
+      </c>
+      <c r="E56" t="s">
+        <v>115</v>
+      </c>
+      <c r="F56">
+        <f>-4/-0.2</f>
+        <v>20</v>
+      </c>
+      <c r="J56" s="31">
+        <v>-0.35000000000000009</v>
+      </c>
+      <c r="K56" s="31">
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="L56" s="31">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="O56" s="31">
+        <v>-0.35000000000000009</v>
+      </c>
+      <c r="P56" s="31">
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="Q56" s="31">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="57" spans="2:17">
+      <c r="B57" s="1">
+        <v>2</v>
+      </c>
+      <c r="C57" t="s">
+        <v>113</v>
+      </c>
+      <c r="E57" t="s">
+        <v>116</v>
+      </c>
+      <c r="F57" s="22">
+        <f>-6/0.45</f>
+        <v>-13.333333333333332</v>
+      </c>
+    </row>
+    <row r="58" spans="2:17">
+      <c r="B58" s="1">
+        <v>3</v>
+      </c>
+      <c r="C58" t="s">
+        <v>114</v>
+      </c>
+      <c r="E58" t="s">
+        <v>116</v>
+      </c>
+      <c r="F58">
+        <f>-4/0.05</f>
+        <v>-80</v>
+      </c>
+      <c r="J58" s="22" cm="1">
+        <f t="array" ref="J58:J60">MMULT(J54:L56,K49:K51)</f>
+        <v>6.6666666666666696</v>
+      </c>
+      <c r="O58" s="22" cm="1">
+        <f t="array" ref="O58:O60">MMULT(O54:Q56,P49:P51)</f>
+        <v>3.5527136788005009E-15</v>
+      </c>
+    </row>
+    <row r="59" spans="2:17">
+      <c r="D59" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="F59" s="22">
+        <f>F57</f>
+        <v>-13.333333333333332</v>
+      </c>
+      <c r="G59" t="s">
+        <v>117</v>
+      </c>
+      <c r="H59">
+        <f>F56</f>
+        <v>20</v>
+      </c>
+      <c r="J59" s="22">
+        <v>-4.4408920985006262E-16</v>
+      </c>
+      <c r="O59" s="22">
+        <v>14.999999999999996</v>
+      </c>
+    </row>
+    <row r="60" spans="2:17">
+      <c r="J60" s="22">
+        <v>3.3333333333333304</v>
+      </c>
+      <c r="O60" s="22">
+        <v>4.9999999999999982</v>
+      </c>
+    </row>
+    <row r="61" spans="2:17">
+      <c r="B61" t="s">
+        <v>118</v>
+      </c>
+      <c r="J61" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="K61" s="32">
+        <f>32*J60+24*J59+48*J58</f>
+        <v>426.66666666666669</v>
+      </c>
+      <c r="O61" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="P61" s="33">
+        <f>32*O60+24*O59+48*O58</f>
+        <v>520</v>
+      </c>
+    </row>
+    <row r="62" spans="2:17">
+      <c r="B62" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="D62" s="32">
+        <f>C48+F59</f>
+        <v>16.666666666666668</v>
+      </c>
+    </row>
+    <row r="63" spans="2:17">
+      <c r="B63" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="D63" s="33">
+        <f>C48+H59</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17">
+      <c r="B65" s="30" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17">
+      <c r="E67" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="F67" s="4">
+        <v>40</v>
+      </c>
+      <c r="J67" t="s">
+        <v>135</v>
+      </c>
+      <c r="K67">
+        <v>40</v>
+      </c>
+      <c r="O67" t="s">
+        <v>136</v>
+      </c>
+      <c r="P67">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="68" spans="2:17">
+      <c r="B68" s="31">
+        <v>0.40000000000000008</v>
+      </c>
+      <c r="C68" s="31">
+        <v>-0.2</v>
+      </c>
+      <c r="D68" s="31">
+        <v>-0.2</v>
+      </c>
+      <c r="F68" s="4">
+        <v>30</v>
+      </c>
+      <c r="K68">
+        <v>30</v>
+      </c>
+      <c r="P68">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17">
+      <c r="B69" s="31">
+        <v>-0.15000000000000002</v>
+      </c>
+      <c r="C69" s="31">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="D69" s="31">
+        <v>-4.9999999999999989E-2</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="K69" s="22">
+        <f>D79</f>
+        <v>22.727272727272727</v>
+      </c>
+      <c r="P69">
+        <f>D80</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17">
+      <c r="B70" s="31">
+        <v>-0.35000000000000009</v>
+      </c>
+      <c r="C70" s="31">
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="D70" s="31">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17">
+      <c r="J71" s="31">
+        <v>0.40000000000000008</v>
+      </c>
+      <c r="K71" s="31">
+        <v>-0.2</v>
+      </c>
+      <c r="L71" s="31">
+        <v>-0.2</v>
+      </c>
+      <c r="O71" s="31">
+        <v>0.40000000000000008</v>
+      </c>
+      <c r="P71" s="31">
+        <v>-0.2</v>
+      </c>
+      <c r="Q71" s="31">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17">
+      <c r="C72" t="s">
+        <v>100</v>
+      </c>
+      <c r="J72" s="31">
+        <v>-0.15000000000000002</v>
+      </c>
+      <c r="K72" s="31">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="L72" s="31">
+        <v>-4.9999999999999989E-2</v>
+      </c>
+      <c r="O72" s="31">
+        <v>-0.15000000000000002</v>
+      </c>
+      <c r="P72" s="31">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="Q72" s="31">
+        <v>-4.9999999999999989E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17">
+      <c r="B73" s="1">
+        <v>1</v>
+      </c>
+      <c r="C73">
+        <f>B68*F67+C68*F68+30*D68</f>
+        <v>4.0000000000000036</v>
+      </c>
+      <c r="D73" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="E73" t="s">
+        <v>123</v>
+      </c>
+      <c r="F73" t="s">
+        <v>126</v>
+      </c>
+      <c r="G73">
+        <f>-4/-0.2</f>
+        <v>20</v>
+      </c>
+      <c r="J73" s="31">
+        <v>-0.35000000000000009</v>
+      </c>
+      <c r="K73" s="31">
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="L73" s="31">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="O73" s="31">
+        <v>-0.35000000000000009</v>
+      </c>
+      <c r="P73" s="31">
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="Q73" s="31">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17">
+      <c r="B74" s="1">
+        <v>2</v>
+      </c>
+      <c r="C74">
+        <f>B69*F67+C69*F68+D69*30</f>
+        <v>5.9999999999999982</v>
+      </c>
+      <c r="D74" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="E74" t="s">
+        <v>123</v>
+      </c>
+      <c r="F74" t="s">
+        <v>126</v>
+      </c>
+      <c r="G74">
+        <f>-6/-0.05</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17">
+      <c r="B75" s="1">
+        <v>3</v>
+      </c>
+      <c r="C75">
+        <f>B70*F67+C70*F68+D70*30</f>
+        <v>3.9999999999999982</v>
+      </c>
+      <c r="D75" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="E75" t="s">
+        <v>123</v>
+      </c>
+      <c r="F75" t="s">
+        <v>127</v>
+      </c>
+      <c r="G75" s="22">
+        <f>-4/0.55</f>
+        <v>-7.2727272727272725</v>
+      </c>
+      <c r="J75" s="22" cm="1">
+        <f t="array" ref="J75:J77">MMULT(J71:L73,K67:K69)</f>
+        <v>5.4545454545454577</v>
+      </c>
+      <c r="O75" s="22" cm="1">
+        <f t="array" ref="O75:O77">MMULT(O71:Q73,P67:P69)</f>
+        <v>3.5527136788005009E-15</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17">
+      <c r="E76" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="F76" s="30"/>
+      <c r="J76" s="22">
+        <v>6.3636363636363615</v>
+      </c>
+      <c r="O76" s="22">
+        <v>4.9999999999999982</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17">
+      <c r="E77" s="22">
+        <f>G75</f>
+        <v>-7.2727272727272725</v>
+      </c>
+      <c r="F77" t="s">
+        <v>128</v>
+      </c>
+      <c r="G77">
+        <f>G73</f>
+        <v>20</v>
+      </c>
+      <c r="J77" s="22">
+        <v>-1.7763568394002505E-15</v>
+      </c>
+      <c r="O77" s="22">
+        <v>15.000000000000002</v>
+      </c>
+    </row>
+    <row r="78" spans="2:17">
+      <c r="B78" t="s">
+        <v>129</v>
+      </c>
+      <c r="J78" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="K78" s="32">
+        <f>32*J77+24*J76+48*J75</f>
+        <v>414.54545454545462</v>
+      </c>
+      <c r="O78" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="P78" s="33">
+        <f>O77*32+24*O76+48*O75</f>
+        <v>600.00000000000023</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17">
+      <c r="B79" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="D79" s="32">
+        <f>30+E77</f>
+        <v>22.727272727272727</v>
+      </c>
+    </row>
+    <row r="80" spans="2:17">
+      <c r="B80" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="D80" s="33">
+        <f>30+G77</f>
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>